--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92562876006</v>
+        <v>46157.93074091709</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93074091709</v>
+        <v>46157.93156973249</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93156973249</v>
+        <v>46157.9339454346</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9339454346</v>
+        <v>46157.93710330395</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93710330395</v>
+        <v>46158.28211476017</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28211476017</v>
+        <v>46158.29667370117</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29667370117</v>
+        <v>46158.29806973235</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29806973235</v>
+        <v>46158.33382307642</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33382307642</v>
+        <v>46158.36849616939</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36849616939</v>
+        <v>46158.37282426644</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
